--- a/models/[2026-05-25] Salesforce Model.xlsx
+++ b/models/[2026-05-25] Salesforce Model.xlsx
@@ -3552,7 +3552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:Q62"/>
+  <dimension ref="B2:Q65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.7109375" customWidth="1" min="1" max="1"/>
@@ -3591,8 +3591,8 @@
           <t>Bear</t>
         </is>
       </c>
-      <c r="P5" s="6" t="n">
-        <v>96.21447082229568</v>
+      <c r="P5" s="6">
+        <f>D26</f>
       </c>
       <c r="Q5" s="15" t="inlineStr">
         <is>
@@ -3606,8 +3606,8 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="P6" s="6" t="n">
-        <v>287.3368002885888</v>
+      <c r="P6" s="6">
+        <f>D45</f>
       </c>
       <c r="Q6" s="15" t="inlineStr">
         <is>
@@ -3621,8 +3621,8 @@
           <t>Bull</t>
         </is>
       </c>
-      <c r="P7" s="6" t="n">
-        <v>521.0165762594767</v>
+      <c r="P7" s="6">
+        <f>D64</f>
       </c>
       <c r="Q7" s="15" t="inlineStr">
         <is>
@@ -4166,1084 +4166,1114 @@
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>10Y price CAGR vs current price</t>
+        </is>
+      </c>
+      <c r="D27" s="19">
+        <f>POWER(D26/Valuation!$C$4,1/10)-1</f>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>Base Case</t>
         </is>
       </c>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="24" t="n"/>
-      <c r="E28" s="24" t="n"/>
-      <c r="F28" s="24" t="n"/>
-      <c r="G28" s="24" t="n"/>
-      <c r="H28" s="24" t="n"/>
-      <c r="I28" s="24" t="n"/>
-      <c r="J28" s="24" t="n"/>
-      <c r="K28" s="24" t="n"/>
-      <c r="L28" s="24" t="n"/>
-      <c r="M28" s="25" t="n"/>
-    </row>
-    <row r="29">
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="24" t="n"/>
+      <c r="I29" s="24" t="n"/>
+      <c r="J29" s="24" t="n"/>
+      <c r="K29" s="24" t="n"/>
+      <c r="L29" s="24" t="n"/>
+      <c r="M29" s="25" t="n"/>
+    </row>
+    <row r="30">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>FY2026A</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>FY2031E</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>FY2032E</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>FY2033E</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>FY2034E</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>FY2035E</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>FY2036E</t>
         </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Revenue growth</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="E30" s="19" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="F30" s="19" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="G30" s="19" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="H30" s="19" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="I30" s="19" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="J30" s="19" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="K30" s="19" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="L30" s="19" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M30" s="19" t="n">
-        <v>0.038</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="n">
-        <v>41525</v>
-      </c>
-      <c r="D31" s="18">
-        <f>C31*(1+D30)</f>
-        <v/>
-      </c>
-      <c r="E31" s="18">
-        <f>D31*(1+E30)</f>
-        <v/>
-      </c>
-      <c r="F31" s="18">
-        <f>E31*(1+F30)</f>
-        <v/>
-      </c>
-      <c r="G31" s="18">
-        <f>F31*(1+G30)</f>
-        <v/>
-      </c>
-      <c r="H31" s="18">
-        <f>G31*(1+H30)</f>
-        <v/>
-      </c>
-      <c r="I31" s="18">
-        <f>H31*(1+I30)</f>
-        <v/>
-      </c>
-      <c r="J31" s="18">
-        <f>I31*(1+J30)</f>
-        <v/>
-      </c>
-      <c r="K31" s="18">
-        <f>J31*(1+K30)</f>
-        <v/>
-      </c>
-      <c r="L31" s="18">
-        <f>K31*(1+L30)</f>
-        <v/>
-      </c>
-      <c r="M31" s="18">
-        <f>L31*(1+M30)</f>
-        <v/>
+          <t>Revenue growth</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="E31" s="19" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J31" s="19" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="K31" s="19" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="L31" s="19" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M31" s="19" t="n">
+        <v>0.038</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Reported FCF margin</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E32" s="19" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="F32" s="19" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="G32" s="19" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="H32" s="19" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="I32" s="19" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J32" s="19" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K32" s="19" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="L32" s="19" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M32" s="19" t="n">
-        <v>0.35</v>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>41525</v>
+      </c>
+      <c r="D32" s="18">
+        <f>C32*(1+D31)</f>
+        <v/>
+      </c>
+      <c r="E32" s="18">
+        <f>D32*(1+E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="18">
+        <f>E32*(1+F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="18">
+        <f>F32*(1+G31)</f>
+        <v/>
+      </c>
+      <c r="H32" s="18">
+        <f>G32*(1+H31)</f>
+        <v/>
+      </c>
+      <c r="I32" s="18">
+        <f>H32*(1+I31)</f>
+        <v/>
+      </c>
+      <c r="J32" s="18">
+        <f>I32*(1+J31)</f>
+        <v/>
+      </c>
+      <c r="K32" s="18">
+        <f>J32*(1+K31)</f>
+        <v/>
+      </c>
+      <c r="L32" s="18">
+        <f>K32*(1+L31)</f>
+        <v/>
+      </c>
+      <c r="M32" s="18">
+        <f>L32*(1+M31)</f>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Reported FCF</t>
-        </is>
-      </c>
-      <c r="D33" s="18">
-        <f>D31*D32</f>
-        <v/>
-      </c>
-      <c r="E33" s="18">
-        <f>E31*E32</f>
-        <v/>
-      </c>
-      <c r="F33" s="18">
-        <f>F31*F32</f>
-        <v/>
-      </c>
-      <c r="G33" s="18">
-        <f>G31*G32</f>
-        <v/>
-      </c>
-      <c r="H33" s="18">
-        <f>H31*H32</f>
-        <v/>
-      </c>
-      <c r="I33" s="18">
-        <f>I31*I32</f>
-        <v/>
-      </c>
-      <c r="J33" s="18">
-        <f>J31*J32</f>
-        <v/>
-      </c>
-      <c r="K33" s="18">
-        <f>K31*K32</f>
-        <v/>
-      </c>
-      <c r="L33" s="18">
-        <f>L31*L32</f>
-        <v/>
-      </c>
-      <c r="M33" s="18">
-        <f>M31*M32</f>
-        <v/>
+          <t>Reported FCF margin</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E33" s="19" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="G33" s="19" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="I33" s="19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J33" s="19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K33" s="19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L33" s="19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M33" s="19" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>SBC % revenue</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="E34" s="19" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="F34" s="19" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="G34" s="19" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="H34" s="19" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="I34" s="19" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="J34" s="19" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="K34" s="19" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L34" s="19" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M34" s="19" t="n">
-        <v>0.06</v>
+          <t>Reported FCF</t>
+        </is>
+      </c>
+      <c r="D34" s="18">
+        <f>D32*D33</f>
+        <v/>
+      </c>
+      <c r="E34" s="18">
+        <f>E32*E33</f>
+        <v/>
+      </c>
+      <c r="F34" s="18">
+        <f>F32*F33</f>
+        <v/>
+      </c>
+      <c r="G34" s="18">
+        <f>G32*G33</f>
+        <v/>
+      </c>
+      <c r="H34" s="18">
+        <f>H32*H33</f>
+        <v/>
+      </c>
+      <c r="I34" s="18">
+        <f>I32*I33</f>
+        <v/>
+      </c>
+      <c r="J34" s="18">
+        <f>J32*J33</f>
+        <v/>
+      </c>
+      <c r="K34" s="18">
+        <f>K32*K33</f>
+        <v/>
+      </c>
+      <c r="L34" s="18">
+        <f>L32*L33</f>
+        <v/>
+      </c>
+      <c r="M34" s="18">
+        <f>M32*M33</f>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>SBC</t>
-        </is>
-      </c>
-      <c r="D35" s="18">
-        <f>D31*D34</f>
-        <v/>
-      </c>
-      <c r="E35" s="18">
-        <f>E31*E34</f>
-        <v/>
-      </c>
-      <c r="F35" s="18">
-        <f>F31*F34</f>
-        <v/>
-      </c>
-      <c r="G35" s="18">
-        <f>G31*G34</f>
-        <v/>
-      </c>
-      <c r="H35" s="18">
-        <f>H31*H34</f>
-        <v/>
-      </c>
-      <c r="I35" s="18">
-        <f>I31*I34</f>
-        <v/>
-      </c>
-      <c r="J35" s="18">
-        <f>J31*J34</f>
-        <v/>
-      </c>
-      <c r="K35" s="18">
-        <f>K31*K34</f>
-        <v/>
-      </c>
-      <c r="L35" s="18">
-        <f>L31*L34</f>
-        <v/>
-      </c>
-      <c r="M35" s="18">
-        <f>M31*M34</f>
-        <v/>
+          <t>SBC % revenue</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="I35" s="19" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="J35" s="19" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L35" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M35" s="19" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Owner FCF</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="D36" s="18">
-        <f>D33-D35</f>
+        <f>D32*D35</f>
         <v/>
       </c>
       <c r="E36" s="18">
-        <f>E33-E35</f>
+        <f>E32*E35</f>
         <v/>
       </c>
       <c r="F36" s="18">
-        <f>F33-F35</f>
+        <f>F32*F35</f>
         <v/>
       </c>
       <c r="G36" s="18">
-        <f>G33-G35</f>
+        <f>G32*G35</f>
         <v/>
       </c>
       <c r="H36" s="18">
-        <f>H33-H35</f>
+        <f>H32*H35</f>
         <v/>
       </c>
       <c r="I36" s="18">
-        <f>I33-I35</f>
+        <f>I32*I35</f>
         <v/>
       </c>
       <c r="J36" s="18">
-        <f>J33-J35</f>
+        <f>J32*J35</f>
         <v/>
       </c>
       <c r="K36" s="18">
-        <f>K33-K35</f>
+        <f>K32*K35</f>
         <v/>
       </c>
       <c r="L36" s="18">
-        <f>L33-L35</f>
+        <f>L32*L35</f>
         <v/>
       </c>
       <c r="M36" s="18">
-        <f>M33-M35</f>
+        <f>M32*M35</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="D37" s="20">
-        <f>1/(1+D40)^1</f>
-        <v/>
-      </c>
-      <c r="E37" s="20">
-        <f>1/(1+D40)^2</f>
-        <v/>
-      </c>
-      <c r="F37" s="20">
-        <f>1/(1+D40)^3</f>
-        <v/>
-      </c>
-      <c r="G37" s="20">
-        <f>1/(1+D40)^4</f>
-        <v/>
-      </c>
-      <c r="H37" s="20">
-        <f>1/(1+D40)^5</f>
-        <v/>
-      </c>
-      <c r="I37" s="20">
-        <f>1/(1+D40)^6</f>
-        <v/>
-      </c>
-      <c r="J37" s="20">
-        <f>1/(1+D40)^7</f>
-        <v/>
-      </c>
-      <c r="K37" s="20">
-        <f>1/(1+D40)^8</f>
-        <v/>
-      </c>
-      <c r="L37" s="20">
-        <f>1/(1+D40)^9</f>
-        <v/>
-      </c>
-      <c r="M37" s="20">
-        <f>1/(1+D40)^10</f>
+          <t>Owner FCF</t>
+        </is>
+      </c>
+      <c r="D37" s="18">
+        <f>D34-D36</f>
+        <v/>
+      </c>
+      <c r="E37" s="18">
+        <f>E34-E36</f>
+        <v/>
+      </c>
+      <c r="F37" s="18">
+        <f>F34-F36</f>
+        <v/>
+      </c>
+      <c r="G37" s="18">
+        <f>G34-G36</f>
+        <v/>
+      </c>
+      <c r="H37" s="18">
+        <f>H34-H36</f>
+        <v/>
+      </c>
+      <c r="I37" s="18">
+        <f>I34-I36</f>
+        <v/>
+      </c>
+      <c r="J37" s="18">
+        <f>J34-J36</f>
+        <v/>
+      </c>
+      <c r="K37" s="18">
+        <f>K34-K36</f>
+        <v/>
+      </c>
+      <c r="L37" s="18">
+        <f>L34-L36</f>
+        <v/>
+      </c>
+      <c r="M37" s="18">
+        <f>M34-M36</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>PV owner FCF</t>
-        </is>
-      </c>
-      <c r="D38" s="18">
-        <f>D36*D37</f>
-        <v/>
-      </c>
-      <c r="E38" s="18">
-        <f>E36*E37</f>
-        <v/>
-      </c>
-      <c r="F38" s="18">
-        <f>F36*F37</f>
-        <v/>
-      </c>
-      <c r="G38" s="18">
-        <f>G36*G37</f>
-        <v/>
-      </c>
-      <c r="H38" s="18">
-        <f>H36*H37</f>
-        <v/>
-      </c>
-      <c r="I38" s="18">
-        <f>I36*I37</f>
-        <v/>
-      </c>
-      <c r="J38" s="18">
-        <f>J36*J37</f>
-        <v/>
-      </c>
-      <c r="K38" s="18">
-        <f>K36*K37</f>
-        <v/>
-      </c>
-      <c r="L38" s="18">
-        <f>L36*L37</f>
-        <v/>
-      </c>
-      <c r="M38" s="18">
-        <f>M36*M37</f>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="D38" s="20">
+        <f>1/(1+D41)^1</f>
+        <v/>
+      </c>
+      <c r="E38" s="20">
+        <f>1/(1+D41)^2</f>
+        <v/>
+      </c>
+      <c r="F38" s="20">
+        <f>1/(1+D41)^3</f>
+        <v/>
+      </c>
+      <c r="G38" s="20">
+        <f>1/(1+D41)^4</f>
+        <v/>
+      </c>
+      <c r="H38" s="20">
+        <f>1/(1+D41)^5</f>
+        <v/>
+      </c>
+      <c r="I38" s="20">
+        <f>1/(1+D41)^6</f>
+        <v/>
+      </c>
+      <c r="J38" s="20">
+        <f>1/(1+D41)^7</f>
+        <v/>
+      </c>
+      <c r="K38" s="20">
+        <f>1/(1+D41)^8</f>
+        <v/>
+      </c>
+      <c r="L38" s="20">
+        <f>1/(1+D41)^9</f>
+        <v/>
+      </c>
+      <c r="M38" s="20">
+        <f>1/(1+D41)^10</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="D39" s="23" t="n">
-        <v>0.03</v>
+          <t>PV owner FCF</t>
+        </is>
+      </c>
+      <c r="D39" s="18">
+        <f>D37*D38</f>
+        <v/>
+      </c>
+      <c r="E39" s="18">
+        <f>E37*E38</f>
+        <v/>
+      </c>
+      <c r="F39" s="18">
+        <f>F37*F38</f>
+        <v/>
+      </c>
+      <c r="G39" s="18">
+        <f>G37*G38</f>
+        <v/>
+      </c>
+      <c r="H39" s="18">
+        <f>H37*H38</f>
+        <v/>
+      </c>
+      <c r="I39" s="18">
+        <f>I37*I38</f>
+        <v/>
+      </c>
+      <c r="J39" s="18">
+        <f>J37*J38</f>
+        <v/>
+      </c>
+      <c r="K39" s="18">
+        <f>K37*K38</f>
+        <v/>
+      </c>
+      <c r="L39" s="18">
+        <f>L37*L38</f>
+        <v/>
+      </c>
+      <c r="M39" s="18">
+        <f>M37*M38</f>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>WACC</t>
+          <t>Terminal growth</t>
         </is>
       </c>
       <c r="D40" s="23" t="n">
-        <v>0.08912497337890385</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Terminal value</t>
-        </is>
-      </c>
-      <c r="D41" s="18">
-        <f>M36*(1+D39)/(D40-D39)</f>
-        <v/>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="n">
+        <v>0.08912497337890385</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Enterprise value</t>
+          <t>Terminal value</t>
         </is>
       </c>
       <c r="D42" s="18">
-        <f>SUM(D38:M38)+D41/(1+D40)^10</f>
+        <f>M37*(1+D40)/(D41-D40)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Equity value</t>
+          <t>Enterprise value</t>
         </is>
       </c>
       <c r="D43" s="18">
-        <f>D42-Valuation!$C$11</f>
+        <f>SUM(D39:M39)+D42/(1+D41)^10</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="3" t="inlineStr">
         <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="D44" s="18">
+        <f>D43-Valuation!$C$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
           <t>Implied price</t>
         </is>
       </c>
-      <c r="D44" s="13">
-        <f>D43/Valuation!$C$6</f>
+      <c r="D45" s="13">
+        <f>D44/Valuation!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>10Y price CAGR vs current price</t>
+        </is>
+      </c>
+      <c r="D46" s="19">
+        <f>POWER(D45/Valuation!$C$4,1/10)-1</f>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>Bull Case</t>
         </is>
       </c>
-      <c r="C46" s="24" t="n"/>
-      <c r="D46" s="24" t="n"/>
-      <c r="E46" s="24" t="n"/>
-      <c r="F46" s="24" t="n"/>
-      <c r="G46" s="24" t="n"/>
-      <c r="H46" s="24" t="n"/>
-      <c r="I46" s="24" t="n"/>
-      <c r="J46" s="24" t="n"/>
-      <c r="K46" s="24" t="n"/>
-      <c r="L46" s="24" t="n"/>
-      <c r="M46" s="25" t="n"/>
-    </row>
-    <row r="47">
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="24" t="n"/>
+      <c r="D48" s="24" t="n"/>
+      <c r="E48" s="24" t="n"/>
+      <c r="F48" s="24" t="n"/>
+      <c r="G48" s="24" t="n"/>
+      <c r="H48" s="24" t="n"/>
+      <c r="I48" s="24" t="n"/>
+      <c r="J48" s="24" t="n"/>
+      <c r="K48" s="24" t="n"/>
+      <c r="L48" s="24" t="n"/>
+      <c r="M48" s="25" t="n"/>
+    </row>
+    <row r="49">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>FY2026A</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>FY2031E</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>FY2032E</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>FY2033E</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>FY2034E</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>FY2035E</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>FY2036E</t>
         </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Revenue growth</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="n"/>
-      <c r="D48" s="19" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E48" s="19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="F48" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G48" s="19" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H48" s="19" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I48" s="19" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="J48" s="19" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K48" s="19" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="L48" s="19" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M48" s="19" t="n">
-        <v>0.055</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="n">
-        <v>41525</v>
-      </c>
-      <c r="D49" s="18">
-        <f>C49*(1+D48)</f>
-        <v/>
-      </c>
-      <c r="E49" s="18">
-        <f>D49*(1+E48)</f>
-        <v/>
-      </c>
-      <c r="F49" s="18">
-        <f>E49*(1+F48)</f>
-        <v/>
-      </c>
-      <c r="G49" s="18">
-        <f>F49*(1+G48)</f>
-        <v/>
-      </c>
-      <c r="H49" s="18">
-        <f>G49*(1+H48)</f>
-        <v/>
-      </c>
-      <c r="I49" s="18">
-        <f>H49*(1+I48)</f>
-        <v/>
-      </c>
-      <c r="J49" s="18">
-        <f>I49*(1+J48)</f>
-        <v/>
-      </c>
-      <c r="K49" s="18">
-        <f>J49*(1+K48)</f>
-        <v/>
-      </c>
-      <c r="L49" s="18">
-        <f>K49*(1+L48)</f>
-        <v/>
-      </c>
-      <c r="M49" s="18">
-        <f>L49*(1+M48)</f>
-        <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Reported FCF margin</t>
-        </is>
-      </c>
+          <t>Revenue growth</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="n"/>
       <c r="D50" s="19" t="n">
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="E50" s="19" t="n">
-        <v>0.355</v>
+        <v>0.11</v>
       </c>
       <c r="F50" s="19" t="n">
-        <v>0.36</v>
+        <v>0.1</v>
       </c>
       <c r="G50" s="19" t="n">
-        <v>0.365</v>
+        <v>0.09</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>0.37</v>
+        <v>0.08</v>
       </c>
       <c r="I50" s="19" t="n">
-        <v>0.375</v>
+        <v>0.075</v>
       </c>
       <c r="J50" s="19" t="n">
-        <v>0.378</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K50" s="19" t="n">
-        <v>0.38</v>
+        <v>0.065</v>
       </c>
       <c r="L50" s="19" t="n">
-        <v>0.38</v>
+        <v>0.06</v>
       </c>
       <c r="M50" s="19" t="n">
-        <v>0.38</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Reported FCF</t>
-        </is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="n">
+        <v>41525</v>
       </c>
       <c r="D51" s="18">
-        <f>D49*D50</f>
+        <f>C51*(1+D50)</f>
         <v/>
       </c>
       <c r="E51" s="18">
-        <f>E49*E50</f>
+        <f>D51*(1+E50)</f>
         <v/>
       </c>
       <c r="F51" s="18">
-        <f>F49*F50</f>
+        <f>E51*(1+F50)</f>
         <v/>
       </c>
       <c r="G51" s="18">
-        <f>G49*G50</f>
+        <f>F51*(1+G50)</f>
         <v/>
       </c>
       <c r="H51" s="18">
-        <f>H49*H50</f>
+        <f>G51*(1+H50)</f>
         <v/>
       </c>
       <c r="I51" s="18">
-        <f>I49*I50</f>
+        <f>H51*(1+I50)</f>
         <v/>
       </c>
       <c r="J51" s="18">
-        <f>J49*J50</f>
+        <f>I51*(1+J50)</f>
         <v/>
       </c>
       <c r="K51" s="18">
-        <f>K49*K50</f>
+        <f>J51*(1+K50)</f>
         <v/>
       </c>
       <c r="L51" s="18">
-        <f>L49*L50</f>
+        <f>K51*(1+L50)</f>
         <v/>
       </c>
       <c r="M51" s="18">
-        <f>M49*M50</f>
+        <f>L51*(1+M50)</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>SBC % revenue</t>
+          <t>Reported FCF margin</t>
         </is>
       </c>
       <c r="D52" s="19" t="n">
-        <v>0.078</v>
+        <v>0.35</v>
       </c>
       <c r="E52" s="19" t="n">
-        <v>0.073</v>
+        <v>0.355</v>
       </c>
       <c r="F52" s="19" t="n">
-        <v>0.068</v>
+        <v>0.36</v>
       </c>
       <c r="G52" s="19" t="n">
-        <v>0.064</v>
+        <v>0.365</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>0.06</v>
+        <v>0.37</v>
       </c>
       <c r="I52" s="19" t="n">
-        <v>0.057</v>
+        <v>0.375</v>
       </c>
       <c r="J52" s="19" t="n">
-        <v>0.054</v>
+        <v>0.378</v>
       </c>
       <c r="K52" s="19" t="n">
-        <v>0.052</v>
+        <v>0.38</v>
       </c>
       <c r="L52" s="19" t="n">
-        <v>0.05</v>
+        <v>0.38</v>
       </c>
       <c r="M52" s="19" t="n">
-        <v>0.05</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>Reported FCF</t>
         </is>
       </c>
       <c r="D53" s="18">
-        <f>D49*D52</f>
+        <f>D51*D52</f>
         <v/>
       </c>
       <c r="E53" s="18">
-        <f>E49*E52</f>
+        <f>E51*E52</f>
         <v/>
       </c>
       <c r="F53" s="18">
-        <f>F49*F52</f>
+        <f>F51*F52</f>
         <v/>
       </c>
       <c r="G53" s="18">
-        <f>G49*G52</f>
+        <f>G51*G52</f>
         <v/>
       </c>
       <c r="H53" s="18">
-        <f>H49*H52</f>
+        <f>H51*H52</f>
         <v/>
       </c>
       <c r="I53" s="18">
-        <f>I49*I52</f>
+        <f>I51*I52</f>
         <v/>
       </c>
       <c r="J53" s="18">
-        <f>J49*J52</f>
+        <f>J51*J52</f>
         <v/>
       </c>
       <c r="K53" s="18">
-        <f>K49*K52</f>
+        <f>K51*K52</f>
         <v/>
       </c>
       <c r="L53" s="18">
-        <f>L49*L52</f>
+        <f>L51*L52</f>
         <v/>
       </c>
       <c r="M53" s="18">
-        <f>M49*M52</f>
+        <f>M51*M52</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Owner FCF</t>
-        </is>
-      </c>
-      <c r="D54" s="18">
-        <f>D51-D53</f>
-        <v/>
-      </c>
-      <c r="E54" s="18">
-        <f>E51-E53</f>
-        <v/>
-      </c>
-      <c r="F54" s="18">
-        <f>F51-F53</f>
-        <v/>
-      </c>
-      <c r="G54" s="18">
-        <f>G51-G53</f>
-        <v/>
-      </c>
-      <c r="H54" s="18">
-        <f>H51-H53</f>
-        <v/>
-      </c>
-      <c r="I54" s="18">
-        <f>I51-I53</f>
-        <v/>
-      </c>
-      <c r="J54" s="18">
-        <f>J51-J53</f>
-        <v/>
-      </c>
-      <c r="K54" s="18">
-        <f>K51-K53</f>
-        <v/>
-      </c>
-      <c r="L54" s="18">
-        <f>L51-L53</f>
-        <v/>
-      </c>
-      <c r="M54" s="18">
-        <f>M51-M53</f>
-        <v/>
+          <t>SBC % revenue</t>
+        </is>
+      </c>
+      <c r="D54" s="19" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="E54" s="19" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="F54" s="19" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="G54" s="19" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="H54" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I54" s="19" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="J54" s="19" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="K54" s="19" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="L54" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M54" s="19" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="D55" s="20">
-        <f>1/(1+D58)^1</f>
-        <v/>
-      </c>
-      <c r="E55" s="20">
-        <f>1/(1+D58)^2</f>
-        <v/>
-      </c>
-      <c r="F55" s="20">
-        <f>1/(1+D58)^3</f>
-        <v/>
-      </c>
-      <c r="G55" s="20">
-        <f>1/(1+D58)^4</f>
-        <v/>
-      </c>
-      <c r="H55" s="20">
-        <f>1/(1+D58)^5</f>
-        <v/>
-      </c>
-      <c r="I55" s="20">
-        <f>1/(1+D58)^6</f>
-        <v/>
-      </c>
-      <c r="J55" s="20">
-        <f>1/(1+D58)^7</f>
-        <v/>
-      </c>
-      <c r="K55" s="20">
-        <f>1/(1+D58)^8</f>
-        <v/>
-      </c>
-      <c r="L55" s="20">
-        <f>1/(1+D58)^9</f>
-        <v/>
-      </c>
-      <c r="M55" s="20">
-        <f>1/(1+D58)^10</f>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="D55" s="18">
+        <f>D51*D54</f>
+        <v/>
+      </c>
+      <c r="E55" s="18">
+        <f>E51*E54</f>
+        <v/>
+      </c>
+      <c r="F55" s="18">
+        <f>F51*F54</f>
+        <v/>
+      </c>
+      <c r="G55" s="18">
+        <f>G51*G54</f>
+        <v/>
+      </c>
+      <c r="H55" s="18">
+        <f>H51*H54</f>
+        <v/>
+      </c>
+      <c r="I55" s="18">
+        <f>I51*I54</f>
+        <v/>
+      </c>
+      <c r="J55" s="18">
+        <f>J51*J54</f>
+        <v/>
+      </c>
+      <c r="K55" s="18">
+        <f>K51*K54</f>
+        <v/>
+      </c>
+      <c r="L55" s="18">
+        <f>L51*L54</f>
+        <v/>
+      </c>
+      <c r="M55" s="18">
+        <f>M51*M54</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>PV owner FCF</t>
+          <t>Owner FCF</t>
         </is>
       </c>
       <c r="D56" s="18">
-        <f>D54*D55</f>
+        <f>D53-D55</f>
         <v/>
       </c>
       <c r="E56" s="18">
-        <f>E54*E55</f>
+        <f>E53-E55</f>
         <v/>
       </c>
       <c r="F56" s="18">
-        <f>F54*F55</f>
+        <f>F53-F55</f>
         <v/>
       </c>
       <c r="G56" s="18">
-        <f>G54*G55</f>
+        <f>G53-G55</f>
         <v/>
       </c>
       <c r="H56" s="18">
-        <f>H54*H55</f>
+        <f>H53-H55</f>
         <v/>
       </c>
       <c r="I56" s="18">
-        <f>I54*I55</f>
+        <f>I53-I55</f>
         <v/>
       </c>
       <c r="J56" s="18">
-        <f>J54*J55</f>
+        <f>J53-J55</f>
         <v/>
       </c>
       <c r="K56" s="18">
-        <f>K54*K55</f>
+        <f>K53-K55</f>
         <v/>
       </c>
       <c r="L56" s="18">
-        <f>L54*L55</f>
+        <f>L53-L55</f>
         <v/>
       </c>
       <c r="M56" s="18">
-        <f>M54*M55</f>
+        <f>M53-M55</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="D57" s="23" t="n">
-        <v>0.035</v>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="D57" s="20">
+        <f>1/(1+D60)^1</f>
+        <v/>
+      </c>
+      <c r="E57" s="20">
+        <f>1/(1+D60)^2</f>
+        <v/>
+      </c>
+      <c r="F57" s="20">
+        <f>1/(1+D60)^3</f>
+        <v/>
+      </c>
+      <c r="G57" s="20">
+        <f>1/(1+D60)^4</f>
+        <v/>
+      </c>
+      <c r="H57" s="20">
+        <f>1/(1+D60)^5</f>
+        <v/>
+      </c>
+      <c r="I57" s="20">
+        <f>1/(1+D60)^6</f>
+        <v/>
+      </c>
+      <c r="J57" s="20">
+        <f>1/(1+D60)^7</f>
+        <v/>
+      </c>
+      <c r="K57" s="20">
+        <f>1/(1+D60)^8</f>
+        <v/>
+      </c>
+      <c r="L57" s="20">
+        <f>1/(1+D60)^9</f>
+        <v/>
+      </c>
+      <c r="M57" s="20">
+        <f>1/(1+D60)^10</f>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="D58" s="23" t="n">
-        <v>0.08</v>
+          <t>PV owner FCF</t>
+        </is>
+      </c>
+      <c r="D58" s="18">
+        <f>D56*D57</f>
+        <v/>
+      </c>
+      <c r="E58" s="18">
+        <f>E56*E57</f>
+        <v/>
+      </c>
+      <c r="F58" s="18">
+        <f>F56*F57</f>
+        <v/>
+      </c>
+      <c r="G58" s="18">
+        <f>G56*G57</f>
+        <v/>
+      </c>
+      <c r="H58" s="18">
+        <f>H56*H57</f>
+        <v/>
+      </c>
+      <c r="I58" s="18">
+        <f>I56*I57</f>
+        <v/>
+      </c>
+      <c r="J58" s="18">
+        <f>J56*J57</f>
+        <v/>
+      </c>
+      <c r="K58" s="18">
+        <f>K56*K57</f>
+        <v/>
+      </c>
+      <c r="L58" s="18">
+        <f>L56*L57</f>
+        <v/>
+      </c>
+      <c r="M58" s="18">
+        <f>M56*M57</f>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Terminal value</t>
-        </is>
-      </c>
-      <c r="D59" s="18">
-        <f>M54*(1+D57)/(D58-D57)</f>
-        <v/>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="n">
+        <v>0.035</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Enterprise value</t>
-        </is>
-      </c>
-      <c r="D60" s="18">
-        <f>SUM(D56:M56)+D59/(1+D58)^10</f>
-        <v/>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="D60" s="23" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Equity value</t>
+          <t>Terminal value</t>
         </is>
       </c>
       <c r="D61" s="18">
-        <f>D60-Valuation!$C$11</f>
+        <f>M56*(1+D59)/(D60-D59)</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="3" t="inlineStr">
         <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="D62" s="18">
+        <f>SUM(D58:M58)+D61/(1+D60)^10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="D63" s="18">
+        <f>D62-Valuation!$C$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
           <t>Implied price</t>
         </is>
       </c>
-      <c r="D62" s="13">
-        <f>D61/Valuation!$C$6</f>
-        <v/>
+      <c r="D64" s="13">
+        <f>D63/Valuation!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>10Y price CAGR vs current price</t>
+        </is>
+      </c>
+      <c r="D65" s="19">
+        <f>POWER(D64/Valuation!$C$4,1/10)-1</f>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:Q2"/>
     <mergeCell ref="B10:M10"/>
-    <mergeCell ref="B46:M46"/>
-    <mergeCell ref="B28:M28"/>
+    <mergeCell ref="B48:M48"/>
+    <mergeCell ref="B29:M29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
